--- a/docs/downloads/04/tbl_cm_act_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_sex_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>20</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,14 +411,8 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -440,7 +428,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
@@ -463,14 +451,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>36.7</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -486,14 +468,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>3.3</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="7">
@@ -504,19 +486,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>12</v>
-      </c>
-      <c r="E7">
-        <v>10.6</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -532,14 +508,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>1.8</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -555,14 +525,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>71</v>
-      </c>
-      <c r="E9">
-        <v>62.8</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -578,14 +542,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D10">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="11">
@@ -601,60 +565,54 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>1.8</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E12">
-        <v>11.1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Ampijoroa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>19.4</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14">
@@ -670,14 +628,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>30.6</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="15">
@@ -693,14 +651,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E15">
-        <v>36.1</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +674,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>2.8</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -734,19 +686,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D17">
         <v>13</v>
       </c>
       <c r="E17">
-        <v>14.9</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="18">
@@ -757,19 +709,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>1.1</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -785,14 +731,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>57</v>
-      </c>
-      <c r="E19">
-        <v>65.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -808,106 +748,94 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E20">
-        <v>18.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="E21">
-        <v>26.9</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>11.5</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E23">
-        <v>38.5</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Marovoay - Bepako</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>6</v>
-      </c>
-      <c r="E24">
-        <v>23.1</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -918,19 +846,13 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>15</v>
-      </c>
-      <c r="E25">
-        <v>13.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -941,19 +863,13 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>84</v>
-      </c>
-      <c r="E26">
-        <v>75.7</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -964,25 +880,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>10.8</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -992,20 +908,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1015,89 +931,77 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>18.2</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>7</v>
-      </c>
-      <c r="E30">
-        <v>31.8</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="E31">
-        <v>22.7</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E32">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1107,20 +1011,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D33">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E33">
-        <v>33</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Marovoay - Madiromiongana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1130,14 +1034,8 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34">
-        <v>2.1</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1148,19 +1046,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D35">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>58.5</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="36">
@@ -1171,25 +1069,25 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36">
-        <v>6.4</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1199,20 +1097,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>22</v>
-      </c>
-      <c r="E37">
-        <v>19.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1222,20 +1114,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D38">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>14.9</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1245,66 +1137,54 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>37</v>
-      </c>
-      <c r="E39">
-        <v>32.5</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D40">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E40">
-        <v>30.7</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>3</v>
-      </c>
-      <c r="E41">
-        <v>2.6</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1314,20 +1194,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D42">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E42">
-        <v>17.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1337,20 +1217,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1360,20 +1240,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D44">
-        <v>267</v>
+        <v>6</v>
       </c>
       <c r="E44">
-        <v>65.90000000000001</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Marovoay - Maroala</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1383,14 +1263,8 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>60</v>
-      </c>
-      <c r="E45">
-        <v>14.8</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1401,19 +1275,266 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>2</v>
-      </c>
-      <c r="E46">
-        <v>0.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>26</v>
+      </c>
+      <c r="E47">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>37</v>
+      </c>
+      <c r="E48">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>35</v>
+      </c>
+      <c r="E50">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>8</v>
+      </c>
+      <c r="E51">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>32</v>
+      </c>
+      <c r="E52">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>12</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>267</v>
+      </c>
+      <c r="E54">
+        <v>65.90000000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>20</v>
+      </c>
+      <c r="E55">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>60</v>
+      </c>
+      <c r="E56">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>14</v>
+      </c>
+      <c r="E57">
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_act_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_sex_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -418,7 +418,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -532,7 +532,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -738,7 +738,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -858,7 +858,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -898,7 +898,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -938,7 +938,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -978,7 +978,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1024,7 +1024,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1087,7 +1087,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1104,7 +1104,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1144,7 +1144,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1184,7 +1184,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1230,7 +1230,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1253,7 +1253,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1356,7 +1356,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1448,7 +1448,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1494,7 +1494,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">

--- a/docs/downloads/04/tbl_cm_act_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_sex_marovoay_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -582,14 +582,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>26</v>
-      </c>
-      <c r="E12">
-        <v>23</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -605,37 +599,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E13">
-        <v>4.4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bepako</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-      <c r="E14">
-        <v>27.8</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -651,14 +639,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>30.6</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="16">
@@ -674,8 +662,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
+      <c r="E16">
+        <v>30.6</v>
       </c>
     </row>
     <row r="17">
@@ -691,14 +685,8 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>13</v>
-      </c>
-      <c r="E17">
-        <v>36.1</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -714,8 +702,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>13</v>
+      </c>
+      <c r="E18">
+        <v>36.1</v>
       </c>
     </row>
     <row r="19">
@@ -726,12 +720,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -748,14 +742,8 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>6</v>
-      </c>
-      <c r="E20">
-        <v>6.9</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -771,14 +759,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D21">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>65.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="22">
@@ -794,8 +782,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>57</v>
+      </c>
+      <c r="E22">
+        <v>65.5</v>
       </c>
     </row>
     <row r="23">
@@ -811,14 +805,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>16</v>
-      </c>
-      <c r="E23">
-        <v>18.4</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -834,24 +822,30 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>16</v>
+      </c>
+      <c r="E24">
+        <v>18.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Madiromiongana</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -868,7 +862,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -885,14 +879,8 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>10</v>
-      </c>
-      <c r="E27">
-        <v>38.5</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -908,14 +896,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <v>23.1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="29">
@@ -931,7 +919,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
@@ -943,13 +931,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>6</v>
+      </c>
+      <c r="E30">
+        <v>23.1</v>
       </c>
     </row>
     <row r="31">
@@ -960,19 +954,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>84</v>
-      </c>
-      <c r="E31">
-        <v>75.7</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -988,14 +976,8 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>7</v>
-      </c>
-      <c r="E32">
-        <v>6.3</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1011,14 +993,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E33">
-        <v>10.8</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="34">
@@ -1034,70 +1016,70 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>7</v>
+      </c>
+      <c r="E34">
+        <v>6.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D35">
-        <v>8</v>
-      </c>
-      <c r="E35">
-        <v>36.4</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E36">
-        <v>31.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maroala</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1114,14 +1096,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>22.7</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="39">
@@ -1137,8 +1119,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>7</v>
+      </c>
+      <c r="E39">
+        <v>31.8</v>
       </c>
     </row>
     <row r="40">
@@ -1149,19 +1137,13 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>20</v>
-      </c>
-      <c r="E40">
-        <v>21.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1172,13 +1154,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>22.7</v>
       </c>
     </row>
     <row r="42">
@@ -1189,19 +1177,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>55</v>
-      </c>
-      <c r="E42">
-        <v>58.5</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1217,14 +1199,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D43">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E43">
-        <v>7.4</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="44">
@@ -1240,14 +1222,8 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>6</v>
-      </c>
-      <c r="E44">
-        <v>6.4</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1263,94 +1239,94 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>55</v>
+      </c>
+      <c r="E45">
+        <v>58.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>7</v>
+      </c>
+      <c r="E46">
+        <v>7.4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>26</v>
-      </c>
-      <c r="E47">
-        <v>22.8</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D48">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E48">
-        <v>32.5</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
-      </c>
-      <c r="D49">
-        <v>5</v>
-      </c>
-      <c r="E49">
-        <v>4.4</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1366,14 +1342,8 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>35</v>
-      </c>
-      <c r="E50">
-        <v>30.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1389,14 +1359,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D51">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E51">
-        <v>7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="52">
@@ -1407,19 +1377,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D52">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E52">
-        <v>7.9</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="53">
@@ -1430,19 +1400,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D53">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="54">
@@ -1453,19 +1423,13 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>267</v>
-      </c>
-      <c r="E54">
-        <v>65.90000000000001</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1476,19 +1440,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D55">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E55">
-        <v>4.9</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="56">
@@ -1499,19 +1463,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D56">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="E56">
-        <v>14.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="57">
@@ -1527,14 +1491,146 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>32</v>
+      </c>
+      <c r="E57">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>12</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>267</v>
+      </c>
+      <c r="E59">
+        <v>65.90000000000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>20</v>
+      </c>
+      <c r="E60">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>60</v>
+      </c>
+      <c r="E62">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>Services &amp; Autres</t>
         </is>
       </c>
-      <c r="D57">
-        <v>14</v>
-      </c>
-      <c r="E57">
-        <v>3.5</v>
+      <c r="D63">
+        <v>10</v>
+      </c>
+      <c r="E63">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
